--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -7936,7 +7936,7 @@
       </c>
       <c r="C105" s="9"/>
       <c r="D105" s="8">
-        <v>46272.1296174537</v>
+        <v>46279.16744278935</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>341</v>
@@ -7999,7 +7999,7 @@
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46227.722511921296</v>
+        <v>46279.167447280095</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>210</v>
@@ -8052,7 +8052,7 @@
       </c>
       <c r="C107" s="9"/>
       <c r="D107" s="8">
-        <v>46227.72251247685</v>
+        <v>46279.16744851852</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>215</v>
@@ -8270,7 +8270,7 @@
       </c>
       <c r="C111" s="9"/>
       <c r="D111" s="8">
-        <v>46223.595232754626</v>
+        <v>46279.13450912037</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>355</v>
@@ -8315,8 +8315,8 @@
       <c r="S111" s="9">
         <v>0</v>
       </c>
-      <c r="T111" s="11" t="s">
-        <v>127</v>
+      <c r="T111" s="12" t="s">
+        <v>238</v>
       </c>
       <c r="U111" s="10" t="s">
         <v>53</v>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -7936,7 +7936,7 @@
       </c>
       <c r="C105" s="9"/>
       <c r="D105" s="8">
-        <v>46279.16744278935</v>
+        <v>46280.14214865741</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>341</v>
@@ -7983,8 +7983,8 @@
       <c r="S105" s="9">
         <v>0</v>
       </c>
-      <c r="T105" s="12" t="s">
-        <v>238</v>
+      <c r="T105" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U105" s="10" t="s">
         <v>53</v>
@@ -8105,7 +8105,7 @@
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46273.13886990741</v>
+        <v>46280.167464976854</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>349</v>
@@ -8168,7 +8168,7 @@
       </c>
       <c r="C109" s="9"/>
       <c r="D109" s="8">
-        <v>46223.59502533565</v>
+        <v>46280.16746697917</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>210</v>
@@ -8219,7 +8219,7 @@
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46223.59502458334</v>
+        <v>46280.1674683912</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>215</v>
@@ -8480,7 +8480,7 @@
       </c>
       <c r="C115" s="9"/>
       <c r="D115" s="8">
-        <v>46114.63723893519</v>
+        <v>46280.126709398144</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>365</v>
@@ -8527,8 +8527,8 @@
       <c r="S115" s="9">
         <v>0</v>
       </c>
-      <c r="T115" s="11" t="s">
-        <v>127</v>
+      <c r="T115" s="12" t="s">
+        <v>238</v>
       </c>
       <c r="U115" s="10" t="s">
         <v>53</v>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -5807,7 +5807,7 @@
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46274.137942905094</v>
+        <v>46281.16738633101</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>234</v>
@@ -5870,7 +5870,7 @@
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46114.62851033565</v>
+        <v>46281.16738878472</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>210</v>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46114.62851040509</v>
+        <v>46281.16739015046</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>242</v>
@@ -8105,7 +8105,7 @@
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46280.167464976854</v>
+        <v>46281.12625642361</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>349</v>
@@ -8152,8 +8152,8 @@
       <c r="S108" s="6">
         <v>0</v>
       </c>
-      <c r="T108" s="12" t="s">
-        <v>238</v>
+      <c r="T108" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U108" s="10" t="s">
         <v>53</v>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -727,361 +727,361 @@
     <t>OT 4287 ZVR 1-14-42/4,OT  4288 ZVR1-14-30/4</t>
   </si>
   <si>
+    <t>1213869987281952</t>
+  </si>
+  <si>
+    <t>Check pruebas FAT,OT 4287 ZVR 1-14-42/4</t>
+  </si>
+  <si>
+    <t>1213869987281953</t>
+  </si>
+  <si>
+    <t>OT  4288 ZVR1-14-30/4</t>
+  </si>
+  <si>
+    <t>Check pruebas FAT,OT 4288 ZVR1-14-30/4</t>
+  </si>
+  <si>
+    <t>1213833622855516</t>
+  </si>
+  <si>
+    <t>Control de calidad</t>
+  </si>
+  <si>
+    <t>Control de calidad Fabricación externa</t>
+  </si>
+  <si>
+    <t>1213833622855625</t>
+  </si>
+  <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
+    <t>Control de calidad,Recepcion Fabricacion externa</t>
+  </si>
+  <si>
+    <t>1213840446207872</t>
+  </si>
+  <si>
+    <t>Bodega</t>
+  </si>
+  <si>
+    <t>Recepcion materiales a codigos // compras locales aprovisionamiento,Control de calidad compras materiales a codigo // compras locale aprovisionamient</t>
+  </si>
+  <si>
+    <t>1213840446207876</t>
+  </si>
+  <si>
+    <t>Recepcion materiales a codigos // compras locales aprovisionamiento</t>
+  </si>
+  <si>
+    <t>Victor Muñoz</t>
+  </si>
+  <si>
+    <t>victor.munoz@zitron.com</t>
+  </si>
+  <si>
+    <t>Control de calidad compras materiales a codigo // compras locale aprovisionamient,Bodega</t>
+  </si>
+  <si>
+    <t>1213840446207878</t>
+  </si>
+  <si>
+    <t>Control de calidad compras materiales a codigo // compras locale aprovisionamient</t>
+  </si>
+  <si>
+    <t>Bodega,Preparacion materiales</t>
+  </si>
+  <si>
+    <t>1213869987281780</t>
+  </si>
+  <si>
+    <t>Caldereria</t>
+  </si>
+  <si>
+    <t>Preparacion materiales,Armado,Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1213869987281782</t>
+  </si>
+  <si>
+    <t>Preparacion materiales</t>
+  </si>
+  <si>
+    <t>Nicolás Mol</t>
+  </si>
+  <si>
+    <t>nicolas.mol@zitron.com</t>
+  </si>
+  <si>
+    <t>Caldereria,OT 4287 ZVR 1-14-42/4,OT 4288 ZVR1-14-30/4</t>
+  </si>
+  <si>
+    <t>1213869987281784</t>
+  </si>
+  <si>
+    <t>Armado</t>
+  </si>
+  <si>
+    <t>Caldereria,Control de calidad Armado  4388</t>
+  </si>
+  <si>
+    <t>1213869987281817</t>
+  </si>
+  <si>
+    <t>Preparacion materiales,Check Planos</t>
+  </si>
+  <si>
+    <t>Armado,OT 4287 ZVR 1-14-42/4</t>
+  </si>
+  <si>
+    <t>1213869987281819</t>
+  </si>
+  <si>
+    <t>Armado,OT 4288 ZVR1-14-30/4</t>
+  </si>
+  <si>
+    <t>1213869987281786</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1213869987281820</t>
+  </si>
+  <si>
+    <t>OT 4287 ZVR 1-14-42/4,Check Planos</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado,OT 4287 ZVR 1-14-42/4</t>
+  </si>
+  <si>
+    <t>1213869987281821</t>
+  </si>
+  <si>
+    <t>OT 4288 ZVR1-14-30/4,Check Planos</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado,OT 4288 ZVR1-14-30/4</t>
+  </si>
+  <si>
+    <t>1213833622855646</t>
+  </si>
+  <si>
+    <t>Bodega:</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe,Recepcion motor,Recepcion Fabricacion externa,Recepcion Rodete,Recepcion Tableros y componentes electricos</t>
+  </si>
+  <si>
+    <t>1213833763304341</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete</t>
+  </si>
+  <si>
+    <t>Bodega:,OT 4287 ZVR 1-14-42/4,OT 4288 ZVR1-14-30/4</t>
+  </si>
+  <si>
+    <t>1213833763304362</t>
+  </si>
+  <si>
+    <t>Bodega:,OT 4290 - TABLERO VDF ABB ACS880-17,OT 4291- TABLERO PLC,OT 4292- TABLERO BOTONERA ,OT 4293-COMPONENTES TABLERO COMPUERTAS</t>
+  </si>
+  <si>
+    <t>1213833806791953</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>Bodega:,OT 4288 ZVR1-14-30/4,OT 4287 ZVR 1-14-42/4</t>
+  </si>
+  <si>
+    <t>1213833564712053</t>
+  </si>
+  <si>
+    <t>Recepcion motor</t>
+  </si>
+  <si>
+    <t>1213833564713244</t>
+  </si>
+  <si>
+    <t>Recepción Sensores</t>
+  </si>
+  <si>
+    <t>1213833564713260</t>
+  </si>
+  <si>
+    <t>Recepcion Fabricacion externa</t>
+  </si>
+  <si>
+    <t>Bodega:,OT 4287 ZVR 1-14-42/4,OT 4288 ZVR1-14-30/4,OT 4288 ZVR1-14-30/4,OT 4287 ZVR 1-14-42/4,OT 4288 ZVR1-14-30/4,OT 4287 ZVR 1-14-42/4,OT 4288 ZVR1-14-30/4,OT 4287 ZVR 1-14-42/4</t>
+  </si>
+  <si>
+    <t>1213832650589422</t>
+  </si>
+  <si>
+    <t>Atenuadores</t>
+  </si>
+  <si>
+    <t>OT 4289 ATENUADORES 3,95X3,97X1,5M</t>
+  </si>
+  <si>
+    <t>1213833777508549</t>
+  </si>
+  <si>
+    <t>Montaje:</t>
+  </si>
+  <si>
+    <t>Montaje Alabe,Revestimiento,Montaje motor,RE-PINTADO,Montaje Rodete,Montaje Sensores,Pruebas FAT</t>
+  </si>
+  <si>
+    <t>1213833777508561</t>
+  </si>
+  <si>
+    <t>Revestimiento</t>
+  </si>
+  <si>
+    <t>1213869987281822</t>
+  </si>
+  <si>
+    <t>OT 4287 ZVR 1-14-42/4,Recepcion Fabricacion externa</t>
+  </si>
+  <si>
+    <t>Revestimiento,OT 4287 ZVR 1-14-42/4</t>
+  </si>
+  <si>
+    <t>1213869987281823</t>
+  </si>
+  <si>
+    <t>OT 4288 ZVR1-14-30/4,Recepcion Fabricacion externa</t>
+  </si>
+  <si>
+    <t>Revestimiento,OT 4288 ZVR1-14-30/4</t>
+  </si>
+  <si>
+    <t>1213833806796991</t>
+  </si>
+  <si>
+    <t>Montaje Sensores</t>
+  </si>
+  <si>
+    <t>1213869987281830</t>
+  </si>
+  <si>
+    <t>Check Planos,Recepción Sensores,OT 4287 ZVR 1-14-42/4</t>
+  </si>
+  <si>
+    <t>Montaje Sensores,OT 4287 ZVR 1-14-42/4</t>
+  </si>
+  <si>
+    <t>1213869987281831</t>
+  </si>
+  <si>
+    <t>Check Planos,Recepción Sensores,OT 4288 ZVR1-14-30/4</t>
+  </si>
+  <si>
+    <t>Montaje Sensores,OT 4288 ZVR1-14-30/4,OT 4288 ZVR1-14-30/4</t>
+  </si>
+  <si>
+    <t>1213833622860576</t>
+  </si>
+  <si>
+    <t>Montaje Alabe</t>
+  </si>
+  <si>
+    <t>1213869987281826</t>
+  </si>
+  <si>
+    <t>Check Planos,Recepcion Alabe,OT 4287 ZVR 1-14-42/4,Recepcion Fabricacion externa</t>
+  </si>
+  <si>
+    <t>Montaje Alabe,OT 4287 ZVR 1-14-42/4</t>
+  </si>
+  <si>
+    <t>1213869987281827</t>
+  </si>
+  <si>
+    <t>Check Planos,OT 4288 ZVR1-14-30/4,Recepcion Fabricacion externa,Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>Montaje Alabe,OT 4288 ZVR1-14-30/4</t>
+  </si>
+  <si>
+    <t>1213833806796736</t>
+  </si>
+  <si>
+    <t>Montaje Rodete</t>
+  </si>
+  <si>
+    <t>1213869987281828</t>
+  </si>
+  <si>
+    <t>OT 4287 ZVR 1-14-42/4,Check Planos,Recepcion Rodete,Recepcion Fabricacion externa</t>
+  </si>
+  <si>
+    <t>1213869987281829</t>
+  </si>
+  <si>
+    <t>OT 4288 ZVR1-14-30/4,Recepcion Rodete,Check Planos,Recepcion Fabricacion externa</t>
+  </si>
+  <si>
+    <t>1213833777509640</t>
+  </si>
+  <si>
+    <t>Montaje motor</t>
+  </si>
+  <si>
+    <t>1213869987281824</t>
+  </si>
+  <si>
+    <t>Check Planos,Recepcion motor,OT 4287 ZVR 1-14-42/4,Recepcion Fabricacion externa</t>
+  </si>
+  <si>
+    <t>Montaje motor,OT 4287 ZVR 1-14-42/4</t>
+  </si>
+  <si>
+    <t>1213869987281825</t>
+  </si>
+  <si>
+    <t>Check Planos,Recepcion motor,OT 4288 ZVR1-14-30/4,Recepcion Fabricacion externa</t>
+  </si>
+  <si>
+    <t>Montaje motor,OT 4288 ZVR1-14-30/4</t>
+  </si>
+  <si>
+    <t>1213833564717704</t>
+  </si>
+  <si>
+    <t>Pruebas FAT</t>
+  </si>
+  <si>
+    <t>1213869987281832</t>
+  </si>
+  <si>
+    <t>Pruebas FAT,OT 4287 ZVR 1-14-42/4</t>
+  </si>
+  <si>
+    <t>1213869987281833</t>
+  </si>
+  <si>
+    <t>Pruebas FAT,OT  4288 ZVR1-14-30/4</t>
+  </si>
+  <si>
+    <t>1213833777515604</t>
+  </si>
+  <si>
+    <t>RE-PINTADO</t>
+  </si>
+  <si>
+    <t>OT 4288 ZVR1-14-30/4,OT 4287 ZVR 1-14-42/4</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1213869987281952</t>
-  </si>
-  <si>
-    <t>Check pruebas FAT,OT 4287 ZVR 1-14-42/4</t>
-  </si>
-  <si>
-    <t>1213869987281953</t>
-  </si>
-  <si>
-    <t>OT  4288 ZVR1-14-30/4</t>
-  </si>
-  <si>
-    <t>Check pruebas FAT,OT 4288 ZVR1-14-30/4</t>
-  </si>
-  <si>
-    <t>1213833622855516</t>
-  </si>
-  <si>
-    <t>Control de calidad</t>
-  </si>
-  <si>
-    <t>Control de calidad Fabricación externa</t>
-  </si>
-  <si>
-    <t>1213833622855625</t>
-  </si>
-  <si>
-    <t>Nicolás López</t>
-  </si>
-  <si>
-    <t>nicolas.lopez@zitron.com</t>
-  </si>
-  <si>
-    <t>Control de calidad,Recepcion Fabricacion externa</t>
-  </si>
-  <si>
-    <t>1213840446207872</t>
-  </si>
-  <si>
-    <t>Bodega</t>
-  </si>
-  <si>
-    <t>Recepcion materiales a codigos // compras locales aprovisionamiento,Control de calidad compras materiales a codigo // compras locale aprovisionamient</t>
-  </si>
-  <si>
-    <t>1213840446207876</t>
-  </si>
-  <si>
-    <t>Recepcion materiales a codigos // compras locales aprovisionamiento</t>
-  </si>
-  <si>
-    <t>Victor Muñoz</t>
-  </si>
-  <si>
-    <t>victor.munoz@zitron.com</t>
-  </si>
-  <si>
-    <t>Control de calidad compras materiales a codigo // compras locale aprovisionamient,Bodega</t>
-  </si>
-  <si>
-    <t>1213840446207878</t>
-  </si>
-  <si>
-    <t>Control de calidad compras materiales a codigo // compras locale aprovisionamient</t>
-  </si>
-  <si>
-    <t>Bodega,Preparacion materiales</t>
-  </si>
-  <si>
-    <t>1213869987281780</t>
-  </si>
-  <si>
-    <t>Caldereria</t>
-  </si>
-  <si>
-    <t>Preparacion materiales,Armado,Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1213869987281782</t>
-  </si>
-  <si>
-    <t>Preparacion materiales</t>
-  </si>
-  <si>
-    <t>Nicolás Mol</t>
-  </si>
-  <si>
-    <t>nicolas.mol@zitron.com</t>
-  </si>
-  <si>
-    <t>Caldereria,OT 4287 ZVR 1-14-42/4,OT 4288 ZVR1-14-30/4</t>
-  </si>
-  <si>
-    <t>1213869987281784</t>
-  </si>
-  <si>
-    <t>Armado</t>
-  </si>
-  <si>
-    <t>Caldereria,Control de calidad Armado  4388</t>
-  </si>
-  <si>
-    <t>1213869987281817</t>
-  </si>
-  <si>
-    <t>Preparacion materiales,Check Planos</t>
-  </si>
-  <si>
-    <t>Armado,OT 4287 ZVR 1-14-42/4</t>
-  </si>
-  <si>
-    <t>1213869987281819</t>
-  </si>
-  <si>
-    <t>Armado,OT 4288 ZVR1-14-30/4</t>
-  </si>
-  <si>
-    <t>1213869987281786</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1213869987281820</t>
-  </si>
-  <si>
-    <t>OT 4287 ZVR 1-14-42/4,Check Planos</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado,OT 4287 ZVR 1-14-42/4</t>
-  </si>
-  <si>
-    <t>1213869987281821</t>
-  </si>
-  <si>
-    <t>OT 4288 ZVR1-14-30/4,Check Planos</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado,OT 4288 ZVR1-14-30/4</t>
-  </si>
-  <si>
-    <t>1213833622855646</t>
-  </si>
-  <si>
-    <t>Bodega:</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe,Recepcion motor,Recepcion Fabricacion externa,Recepcion Rodete,Recepcion Tableros y componentes electricos</t>
-  </si>
-  <si>
-    <t>1213833763304341</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete</t>
-  </si>
-  <si>
-    <t>Bodega:,OT 4287 ZVR 1-14-42/4,OT 4288 ZVR1-14-30/4</t>
-  </si>
-  <si>
-    <t>1213833763304362</t>
-  </si>
-  <si>
-    <t>Bodega:,OT 4290 - TABLERO VDF ABB ACS880-17,OT 4291- TABLERO PLC,OT 4292- TABLERO BOTONERA ,OT 4293-COMPONENTES TABLERO COMPUERTAS</t>
-  </si>
-  <si>
-    <t>1213833806791953</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>Bodega:,OT 4288 ZVR1-14-30/4,OT 4287 ZVR 1-14-42/4</t>
-  </si>
-  <si>
-    <t>1213833564712053</t>
-  </si>
-  <si>
-    <t>Recepcion motor</t>
-  </si>
-  <si>
-    <t>1213833564713244</t>
-  </si>
-  <si>
-    <t>Recepción Sensores</t>
-  </si>
-  <si>
-    <t>1213833564713260</t>
-  </si>
-  <si>
-    <t>Recepcion Fabricacion externa</t>
-  </si>
-  <si>
-    <t>Bodega:,OT 4287 ZVR 1-14-42/4,OT 4288 ZVR1-14-30/4,OT 4288 ZVR1-14-30/4,OT 4287 ZVR 1-14-42/4,OT 4288 ZVR1-14-30/4,OT 4287 ZVR 1-14-42/4,OT 4288 ZVR1-14-30/4,OT 4287 ZVR 1-14-42/4</t>
-  </si>
-  <si>
-    <t>1213832650589422</t>
-  </si>
-  <si>
-    <t>Atenuadores</t>
-  </si>
-  <si>
-    <t>OT 4289 ATENUADORES 3,95X3,97X1,5M</t>
-  </si>
-  <si>
-    <t>1213833777508549</t>
-  </si>
-  <si>
-    <t>Montaje:</t>
-  </si>
-  <si>
-    <t>Montaje Alabe,Revestimiento,Montaje motor,RE-PINTADO,Montaje Rodete,Montaje Sensores,Pruebas FAT</t>
-  </si>
-  <si>
-    <t>1213833777508561</t>
-  </si>
-  <si>
-    <t>Revestimiento</t>
-  </si>
-  <si>
-    <t>1213869987281822</t>
-  </si>
-  <si>
-    <t>OT 4287 ZVR 1-14-42/4,Recepcion Fabricacion externa</t>
-  </si>
-  <si>
-    <t>Revestimiento,OT 4287 ZVR 1-14-42/4</t>
-  </si>
-  <si>
-    <t>1213869987281823</t>
-  </si>
-  <si>
-    <t>OT 4288 ZVR1-14-30/4,Recepcion Fabricacion externa</t>
-  </si>
-  <si>
-    <t>Revestimiento,OT 4288 ZVR1-14-30/4</t>
-  </si>
-  <si>
-    <t>1213833806796991</t>
-  </si>
-  <si>
-    <t>Montaje Sensores</t>
-  </si>
-  <si>
-    <t>1213869987281830</t>
-  </si>
-  <si>
-    <t>Check Planos,Recepción Sensores,OT 4287 ZVR 1-14-42/4</t>
-  </si>
-  <si>
-    <t>Montaje Sensores,OT 4287 ZVR 1-14-42/4</t>
-  </si>
-  <si>
-    <t>1213869987281831</t>
-  </si>
-  <si>
-    <t>Check Planos,Recepción Sensores,OT 4288 ZVR1-14-30/4</t>
-  </si>
-  <si>
-    <t>Montaje Sensores,OT 4288 ZVR1-14-30/4,OT 4288 ZVR1-14-30/4</t>
-  </si>
-  <si>
-    <t>1213833622860576</t>
-  </si>
-  <si>
-    <t>Montaje Alabe</t>
-  </si>
-  <si>
-    <t>1213869987281826</t>
-  </si>
-  <si>
-    <t>Check Planos,Recepcion Alabe,OT 4287 ZVR 1-14-42/4,Recepcion Fabricacion externa</t>
-  </si>
-  <si>
-    <t>Montaje Alabe,OT 4287 ZVR 1-14-42/4</t>
-  </si>
-  <si>
-    <t>1213869987281827</t>
-  </si>
-  <si>
-    <t>Check Planos,OT 4288 ZVR1-14-30/4,Recepcion Fabricacion externa,Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>Montaje Alabe,OT 4288 ZVR1-14-30/4</t>
-  </si>
-  <si>
-    <t>1213833806796736</t>
-  </si>
-  <si>
-    <t>Montaje Rodete</t>
-  </si>
-  <si>
-    <t>1213869987281828</t>
-  </si>
-  <si>
-    <t>OT 4287 ZVR 1-14-42/4,Check Planos,Recepcion Rodete,Recepcion Fabricacion externa</t>
-  </si>
-  <si>
-    <t>1213869987281829</t>
-  </si>
-  <si>
-    <t>OT 4288 ZVR1-14-30/4,Recepcion Rodete,Check Planos,Recepcion Fabricacion externa</t>
-  </si>
-  <si>
-    <t>1213833777509640</t>
-  </si>
-  <si>
-    <t>Montaje motor</t>
-  </si>
-  <si>
-    <t>1213869987281824</t>
-  </si>
-  <si>
-    <t>Check Planos,Recepcion motor,OT 4287 ZVR 1-14-42/4,Recepcion Fabricacion externa</t>
-  </si>
-  <si>
-    <t>Montaje motor,OT 4287 ZVR 1-14-42/4</t>
-  </si>
-  <si>
-    <t>1213869987281825</t>
-  </si>
-  <si>
-    <t>Check Planos,Recepcion motor,OT 4288 ZVR1-14-30/4,Recepcion Fabricacion externa</t>
-  </si>
-  <si>
-    <t>Montaje motor,OT 4288 ZVR1-14-30/4</t>
-  </si>
-  <si>
-    <t>1213833564717704</t>
-  </si>
-  <si>
-    <t>Pruebas FAT</t>
-  </si>
-  <si>
-    <t>1213869987281832</t>
-  </si>
-  <si>
-    <t>Pruebas FAT,OT 4287 ZVR 1-14-42/4</t>
-  </si>
-  <si>
-    <t>1213869987281833</t>
-  </si>
-  <si>
-    <t>Pruebas FAT,OT  4288 ZVR1-14-30/4</t>
-  </si>
-  <si>
-    <t>1213833777515604</t>
-  </si>
-  <si>
-    <t>RE-PINTADO</t>
-  </si>
-  <si>
-    <t>OT 4288 ZVR1-14-30/4,OT 4287 ZVR 1-14-42/4</t>
   </si>
   <si>
     <t>1213869987281834</t>
@@ -5807,7 +5807,7 @@
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46281.16738633101</v>
+        <v>46282.142397662035</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>234</v>
@@ -5854,8 +5854,8 @@
       <c r="S68" s="6">
         <v>0</v>
       </c>
-      <c r="T68" s="12" t="s">
-        <v>238</v>
+      <c r="T68" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="U68" s="10" t="s">
         <v>53</v>
@@ -5863,7 +5863,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B69" s="8">
         <v>46111.55280189815</v>
@@ -5904,7 +5904,7 @@
         <v>210</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q69" s="9"/>
       <c r="R69" s="9"/>
@@ -5914,7 +5914,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B70" s="5">
         <v>46111.55285245371</v>
@@ -5924,7 +5924,7 @@
         <v>46281.16739015046</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -5955,7 +5955,7 @@
         <v>215</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5965,7 +5965,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B71" s="8">
         <v>46108.75714166666</v>
@@ -5975,7 +5975,7 @@
         <v>46118.545566597226</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>25</v>
@@ -5999,7 +5999,7 @@
         <v>26</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="P71" s="9" t="s">
         <v>26</v>
@@ -6012,7 +6012,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B72" s="5">
         <v>46108.75714454861</v>
@@ -6022,16 +6022,16 @@
         <v>46240.16751462963</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>248</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>249</v>
       </c>
       <c r="I72" s="6"/>
       <c r="J72" s="5">
@@ -6047,13 +6047,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="O72" s="6" t="s">
         <v>188</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="Q72" s="5">
         <v>46231</v>
@@ -6073,7 +6073,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B73" s="8">
         <v>46111.50359008102</v>
@@ -6085,7 +6085,7 @@
         <v>46260.58097469907</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>25</v>
@@ -6109,7 +6109,7 @@
         <v>26</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="P73" s="9" t="s">
         <v>26</v>
@@ -6126,7 +6126,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B74" s="5">
         <v>46111.50404616898</v>
@@ -6138,16 +6138,16 @@
         <v>46260.58079141204</v>
       </c>
       <c r="E74" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="F74" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G74" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="F74" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G74" s="6" t="s">
+      <c r="H74" s="6" t="s">
         <v>256</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>257</v>
       </c>
       <c r="I74" s="5">
         <v>46211</v>
@@ -6165,13 +6165,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="O74" s="6" t="s">
         <v>169</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Q74" s="5">
         <v>46211</v>
@@ -6191,7 +6191,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B75" s="8">
         <v>46111.50406170139</v>
@@ -6203,16 +6203,16 @@
         <v>46260.580961342595</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="H75" s="9" t="s">
         <v>248</v>
-      </c>
-      <c r="H75" s="9" t="s">
-        <v>249</v>
       </c>
       <c r="I75" s="8">
         <v>46213</v>
@@ -6230,13 +6230,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="Q75" s="8">
         <v>46213</v>
@@ -6256,7 +6256,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B76" s="5">
         <v>46111.50543856481</v>
@@ -6266,7 +6266,7 @@
         <v>46260.577887962965</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>25</v>
@@ -6290,7 +6290,7 @@
         <v>26</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>26</v>
@@ -6305,7 +6305,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B77" s="8">
         <v>46111.505495046295</v>
@@ -6317,16 +6317,16 @@
         <v>46260.58096115741</v>
       </c>
       <c r="E77" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="F77" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G77" s="9" t="s">
         <v>266</v>
       </c>
-      <c r="F77" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G77" s="9" t="s">
+      <c r="H77" s="9" t="s">
         <v>267</v>
-      </c>
-      <c r="H77" s="9" t="s">
-        <v>268</v>
       </c>
       <c r="I77" s="8">
         <v>46217</v>
@@ -6344,13 +6344,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q77" s="8">
         <v>46217</v>
@@ -6370,7 +6370,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B78" s="5">
         <v>46111.50560314815</v>
@@ -6382,16 +6382,16 @@
         <v>46260.57750302083</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="H78" s="6" t="s">
         <v>267</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>268</v>
       </c>
       <c r="I78" s="5">
         <v>46226</v>
@@ -6409,13 +6409,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O78" s="6" t="s">
         <v>219</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="Q78" s="5">
         <v>46226</v>
@@ -6435,7 +6435,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B79" s="8">
         <v>46111.52633317129</v>
@@ -6453,10 +6453,10 @@
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="H79" s="9" t="s">
         <v>267</v>
-      </c>
-      <c r="H79" s="9" t="s">
-        <v>268</v>
       </c>
       <c r="I79" s="8">
         <v>46226</v>
@@ -6474,13 +6474,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="O79" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="P79" s="9" t="s">
         <v>274</v>
-      </c>
-      <c r="P79" s="9" t="s">
-        <v>275</v>
       </c>
       <c r="Q79" s="9"/>
       <c r="R79" s="9"/>
@@ -6490,7 +6490,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B80" s="5">
         <v>46111.526644375</v>
@@ -6508,10 +6508,10 @@
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="H80" s="6" t="s">
         <v>267</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>268</v>
       </c>
       <c r="I80" s="5">
         <v>46226</v>
@@ -6529,13 +6529,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6545,7 +6545,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B81" s="8">
         <v>46111.50563458333</v>
@@ -6557,16 +6557,16 @@
         <v>46260.57788128473</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="H81" s="9" t="s">
         <v>248</v>
-      </c>
-      <c r="H81" s="9" t="s">
-        <v>249</v>
       </c>
       <c r="I81" s="8">
         <v>46246</v>
@@ -6584,13 +6584,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O81" s="9" t="s">
         <v>219</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q81" s="8">
         <v>46246</v>
@@ -6610,7 +6610,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B82" s="5">
         <v>46111.526916469906</v>
@@ -6628,10 +6628,10 @@
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="H82" s="6" t="s">
         <v>248</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>249</v>
       </c>
       <c r="I82" s="5">
         <v>46246</v>
@@ -6649,13 +6649,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="O82" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="P82" s="6" t="s">
         <v>281</v>
-      </c>
-      <c r="P82" s="6" t="s">
-        <v>282</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6665,7 +6665,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B83" s="8">
         <v>46111.52699828704</v>
@@ -6683,10 +6683,10 @@
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="H83" s="9" t="s">
         <v>248</v>
-      </c>
-      <c r="H83" s="9" t="s">
-        <v>249</v>
       </c>
       <c r="I83" s="8">
         <v>46246</v>
@@ -6704,13 +6704,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="O83" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="P83" s="9" t="s">
         <v>284</v>
-      </c>
-      <c r="P83" s="9" t="s">
-        <v>285</v>
       </c>
       <c r="Q83" s="9"/>
       <c r="R83" s="9"/>
@@ -6720,7 +6720,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B84" s="5">
         <v>46108.75714884259</v>
@@ -6730,7 +6730,7 @@
         <v>46221.1155655787</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>25</v>
@@ -6754,7 +6754,7 @@
         <v>26</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>26</v>
@@ -6767,7 +6767,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B85" s="8">
         <v>46108.75715243055</v>
@@ -6777,16 +6777,16 @@
         <v>46185.184959907405</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="H85" s="9" t="s">
         <v>256</v>
-      </c>
-      <c r="H85" s="9" t="s">
-        <v>257</v>
       </c>
       <c r="I85" s="8">
         <v>46183</v>
@@ -6804,13 +6804,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="O85" s="9" t="s">
         <v>147</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="Q85" s="8">
         <v>46183</v>
@@ -6830,7 +6830,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B86" s="5">
         <v>46108.75715773148</v>
@@ -6846,10 +6846,10 @@
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="H86" s="6" t="s">
         <v>256</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>257</v>
       </c>
       <c r="I86" s="5">
         <v>46239</v>
@@ -6867,13 +6867,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="O86" s="6" t="s">
         <v>138</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="Q86" s="5">
         <v>46239</v>
@@ -6893,7 +6893,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B87" s="8">
         <v>46108.75716349537</v>
@@ -6903,16 +6903,16 @@
         <v>46248.16971915509</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="H87" s="9" t="s">
         <v>256</v>
-      </c>
-      <c r="H87" s="9" t="s">
-        <v>257</v>
       </c>
       <c r="I87" s="8">
         <v>46246</v>
@@ -6930,13 +6930,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="O87" s="9" t="s">
         <v>129</v>
       </c>
       <c r="P87" s="9" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="Q87" s="8">
         <v>46246</v>
@@ -6956,7 +6956,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B88" s="5">
         <v>46108.75716875</v>
@@ -6966,16 +6966,16 @@
         <v>46275.126632685184</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="H88" s="6" t="s">
         <v>256</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>257</v>
       </c>
       <c r="I88" s="5">
         <v>46273</v>
@@ -6993,13 +6993,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="O88" s="6" t="s">
         <v>156</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="Q88" s="5">
         <v>46273</v>
@@ -7019,7 +7019,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B89" s="8">
         <v>46108.75717430556</v>
@@ -7029,16 +7029,16 @@
         <v>46224.18129432871</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="H89" s="9" t="s">
         <v>256</v>
-      </c>
-      <c r="H89" s="9" t="s">
-        <v>257</v>
       </c>
       <c r="I89" s="8">
         <v>46220</v>
@@ -7056,7 +7056,7 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="O89" s="9" t="s">
         <v>178</v>
@@ -7082,7 +7082,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B90" s="5">
         <v>46108.75717877314</v>
@@ -7092,16 +7092,16 @@
         <v>46240.16751195602</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="H90" s="6" t="s">
         <v>256</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>257</v>
       </c>
       <c r="I90" s="6"/>
       <c r="J90" s="5">
@@ -7117,13 +7117,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="Q90" s="5">
         <v>46231</v>
@@ -7143,7 +7143,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B91" s="8">
         <v>46108.822037094906</v>
@@ -7153,16 +7153,16 @@
         <v>46185.18495945602</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="H91" s="9" t="s">
         <v>256</v>
-      </c>
-      <c r="H91" s="9" t="s">
-        <v>257</v>
       </c>
       <c r="I91" s="8">
         <v>46181</v>
@@ -7180,13 +7180,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="O91" s="9" t="s">
         <v>198</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="Q91" s="8">
         <v>46183</v>
@@ -7206,7 +7206,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B92" s="5">
         <v>46108.757183124995</v>
@@ -7216,7 +7216,7 @@
         <v>46221.36615074074</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>25</v>
@@ -7240,7 +7240,7 @@
         <v>26</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>26</v>
@@ -7253,7 +7253,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B93" s="8">
         <v>46108.757186296294</v>
@@ -7263,7 +7263,7 @@
         <v>46268.17428453703</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
@@ -7290,13 +7290,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="O93" s="9" t="s">
         <v>219</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="Q93" s="8">
         <v>46248</v>
@@ -7316,7 +7316,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B94" s="5">
         <v>46111.52720202546</v>
@@ -7353,13 +7353,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="O94" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="P94" s="6" t="s">
         <v>313</v>
-      </c>
-      <c r="P94" s="6" t="s">
-        <v>314</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7369,7 +7369,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B95" s="8">
         <v>46111.52733795139</v>
@@ -7406,13 +7406,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="O95" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="P95" s="9" t="s">
         <v>316</v>
-      </c>
-      <c r="P95" s="9" t="s">
-        <v>317</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -7422,7 +7422,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B96" s="5">
         <v>46108.75720997685</v>
@@ -7432,7 +7432,7 @@
         <v>46270.18529125</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7459,13 +7459,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="O96" s="6" t="s">
         <v>219</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="Q96" s="5">
         <v>46268</v>
@@ -7485,7 +7485,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B97" s="8">
         <v>46111.52790079861</v>
@@ -7522,13 +7522,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="O97" s="9" t="s">
+        <v>320</v>
+      </c>
+      <c r="P97" s="9" t="s">
         <v>321</v>
-      </c>
-      <c r="P97" s="9" t="s">
-        <v>322</v>
       </c>
       <c r="Q97" s="9"/>
       <c r="R97" s="9"/>
@@ -7538,7 +7538,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B98" s="5">
         <v>46111.52796104166</v>
@@ -7575,13 +7575,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="O98" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="P98" s="6" t="s">
         <v>324</v>
-      </c>
-      <c r="P98" s="6" t="s">
-        <v>325</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7591,7 +7591,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B99" s="8">
         <v>46108.75719767361</v>
@@ -7601,7 +7601,7 @@
         <v>46274.149059386575</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
@@ -7628,13 +7628,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="O99" s="9" t="s">
         <v>219</v>
       </c>
       <c r="P99" s="9" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="Q99" s="8">
         <v>46272</v>
@@ -7654,7 +7654,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B100" s="5">
         <v>46111.52756633102</v>
@@ -7691,13 +7691,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="O100" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="P100" s="6" t="s">
         <v>329</v>
-      </c>
-      <c r="P100" s="6" t="s">
-        <v>330</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7707,7 +7707,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B101" s="8">
         <v>46111.527622395835</v>
@@ -7744,13 +7744,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="O101" s="9" t="s">
+        <v>331</v>
+      </c>
+      <c r="P101" s="9" t="s">
         <v>332</v>
-      </c>
-      <c r="P101" s="9" t="s">
-        <v>333</v>
       </c>
       <c r="Q101" s="9"/>
       <c r="R101" s="9"/>
@@ -7760,7 +7760,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B102" s="5">
         <v>46108.75720341435</v>
@@ -7770,7 +7770,7 @@
         <v>46276.143129421296</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7797,13 +7797,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="O102" s="6" t="s">
         <v>219</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="Q102" s="5">
         <v>46274</v>
@@ -7823,7 +7823,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B103" s="8">
         <v>46111.52775804398</v>
@@ -7860,13 +7860,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="P103" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="Q103" s="9"/>
       <c r="R103" s="9"/>
@@ -7876,7 +7876,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B104" s="5">
         <v>46111.52780829861</v>
@@ -7913,13 +7913,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7929,7 +7929,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B105" s="8">
         <v>46108.757191412034</v>
@@ -7939,7 +7939,7 @@
         <v>46280.14214865741</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
@@ -7966,13 +7966,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="9" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="O105" s="9" t="s">
         <v>219</v>
       </c>
       <c r="P105" s="9" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="Q105" s="8">
         <v>46276</v>
@@ -7992,7 +7992,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B106" s="5">
         <v>46111.527446493055</v>
@@ -8029,13 +8029,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="O106" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="P106" s="6" t="s">
         <v>343</v>
-      </c>
-      <c r="P106" s="6" t="s">
-        <v>344</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -8045,7 +8045,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B107" s="8">
         <v>46111.52746010417</v>
@@ -8082,13 +8082,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="9" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="O107" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="P107" s="9" t="s">
         <v>346</v>
-      </c>
-      <c r="P107" s="9" t="s">
-        <v>347</v>
       </c>
       <c r="Q107" s="9"/>
       <c r="R107" s="9"/>
@@ -8098,7 +8098,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B108" s="5">
         <v>46108.757217025464</v>
@@ -8108,7 +8108,7 @@
         <v>46281.12625642361</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -8135,13 +8135,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="O108" s="6" t="s">
         <v>219</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="Q108" s="5">
         <v>46280</v>
@@ -8161,7 +8161,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B109" s="8">
         <v>46111.528031932874</v>
@@ -8196,13 +8196,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="9" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="O109" s="9" t="s">
         <v>210</v>
       </c>
       <c r="P109" s="9" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="Q109" s="9"/>
       <c r="R109" s="9"/>
@@ -8212,7 +8212,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B110" s="5">
         <v>46111.52811128472</v>
@@ -8247,13 +8247,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="O110" s="6" t="s">
         <v>215</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -8263,7 +8263,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B111" s="8">
         <v>46108.75727585648</v>
@@ -8273,7 +8273,7 @@
         <v>46279.13450912037</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
@@ -8298,13 +8298,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="P111" s="9" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="Q111" s="8">
         <v>46286</v>
@@ -8316,7 +8316,7 @@
         <v>0</v>
       </c>
       <c r="T111" s="12" t="s">
-        <v>238</v>
+        <v>356</v>
       </c>
       <c r="U111" s="10" t="s">
         <v>53</v>
@@ -8359,7 +8359,7 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="O112" s="6" t="s">
         <v>210</v>
@@ -8410,10 +8410,10 @@
         <v>26</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="P113" s="9" t="s">
         <v>360</v>
@@ -8528,7 +8528,7 @@
         <v>0</v>
       </c>
       <c r="T115" s="12" t="s">
-        <v>238</v>
+        <v>356</v>
       </c>
       <c r="U115" s="10" t="s">
         <v>53</v>
@@ -8852,7 +8852,7 @@
         <v>46114.628888437495</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -8880,7 +8880,7 @@
         <v>365</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P122" s="6" t="s">
         <v>383</v>
@@ -9284,7 +9284,7 @@
         <v>46223.59535532407</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
@@ -9314,7 +9314,7 @@
         <v>385</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P130" s="6" t="s">
         <v>400</v>
@@ -9343,10 +9343,10 @@
         <v>26</v>
       </c>
       <c r="G131" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="H131" s="9" t="s">
         <v>267</v>
-      </c>
-      <c r="H131" s="9" t="s">
-        <v>268</v>
       </c>
       <c r="I131" s="8">
         <v>46293</v>
@@ -9406,10 +9406,10 @@
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="H132" s="6" t="s">
         <v>267</v>
-      </c>
-      <c r="H132" s="6" t="s">
-        <v>268</v>
       </c>
       <c r="I132" s="6"/>
       <c r="J132" s="5">
@@ -9457,10 +9457,10 @@
         <v>26</v>
       </c>
       <c r="G133" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="H133" s="9" t="s">
         <v>267</v>
-      </c>
-      <c r="H133" s="9" t="s">
-        <v>268</v>
       </c>
       <c r="I133" s="9"/>
       <c r="J133" s="8">
@@ -9508,10 +9508,10 @@
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="H134" s="6" t="s">
         <v>267</v>
-      </c>
-      <c r="H134" s="6" t="s">
-        <v>268</v>
       </c>
       <c r="I134" s="6"/>
       <c r="J134" s="5">
@@ -9559,10 +9559,10 @@
         <v>26</v>
       </c>
       <c r="G135" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="H135" s="9" t="s">
         <v>267</v>
-      </c>
-      <c r="H135" s="9" t="s">
-        <v>268</v>
       </c>
       <c r="I135" s="9"/>
       <c r="J135" s="8">
@@ -9610,10 +9610,10 @@
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="H136" s="6" t="s">
         <v>267</v>
-      </c>
-      <c r="H136" s="6" t="s">
-        <v>268</v>
       </c>
       <c r="I136" s="6"/>
       <c r="J136" s="5">
@@ -9661,10 +9661,10 @@
         <v>26</v>
       </c>
       <c r="G137" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="H137" s="9" t="s">
         <v>267</v>
-      </c>
-      <c r="H137" s="9" t="s">
-        <v>268</v>
       </c>
       <c r="I137" s="9"/>
       <c r="J137" s="8">
@@ -9712,10 +9712,10 @@
         <v>26</v>
       </c>
       <c r="G138" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="H138" s="6" t="s">
         <v>267</v>
-      </c>
-      <c r="H138" s="6" t="s">
-        <v>268</v>
       </c>
       <c r="I138" s="6"/>
       <c r="J138" s="5">
@@ -9734,7 +9734,7 @@
         <v>402</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P138" s="6" t="s">
         <v>418</v>
@@ -9763,10 +9763,10 @@
         <v>26</v>
       </c>
       <c r="G139" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="H139" s="9" t="s">
         <v>267</v>
-      </c>
-      <c r="H139" s="9" t="s">
-        <v>268</v>
       </c>
       <c r="I139" s="8">
         <v>46294</v>
@@ -9826,10 +9826,10 @@
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="H140" s="6" t="s">
         <v>267</v>
-      </c>
-      <c r="H140" s="6" t="s">
-        <v>268</v>
       </c>
       <c r="I140" s="5">
         <v>46294</v>
@@ -9879,10 +9879,10 @@
         <v>26</v>
       </c>
       <c r="G141" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="H141" s="9" t="s">
         <v>267</v>
-      </c>
-      <c r="H141" s="9" t="s">
-        <v>268</v>
       </c>
       <c r="I141" s="8">
         <v>46294</v>
@@ -9932,10 +9932,10 @@
         <v>26</v>
       </c>
       <c r="G142" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="H142" s="6" t="s">
         <v>267</v>
-      </c>
-      <c r="H142" s="6" t="s">
-        <v>268</v>
       </c>
       <c r="I142" s="5">
         <v>46294</v>
@@ -9985,10 +9985,10 @@
         <v>26</v>
       </c>
       <c r="G143" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="H143" s="9" t="s">
         <v>267</v>
-      </c>
-      <c r="H143" s="9" t="s">
-        <v>268</v>
       </c>
       <c r="I143" s="8">
         <v>46294</v>
@@ -10038,10 +10038,10 @@
         <v>26</v>
       </c>
       <c r="G144" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="H144" s="6" t="s">
         <v>267</v>
-      </c>
-      <c r="H144" s="6" t="s">
-        <v>268</v>
       </c>
       <c r="I144" s="5">
         <v>46294</v>
@@ -10091,10 +10091,10 @@
         <v>26</v>
       </c>
       <c r="G145" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="H145" s="9" t="s">
         <v>267</v>
-      </c>
-      <c r="H145" s="9" t="s">
-        <v>268</v>
       </c>
       <c r="I145" s="8">
         <v>46294</v>
@@ -10138,16 +10138,16 @@
         <v>46114.83039427083</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="H146" s="6" t="s">
         <v>267</v>
-      </c>
-      <c r="H146" s="6" t="s">
-        <v>268</v>
       </c>
       <c r="I146" s="5">
         <v>46294</v>

--- a/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
+++ b/data/50001525 - ZITRON PERU METRO LIMA E07.xlsx
@@ -8900,7 +8900,7 @@
       </c>
       <c r="C123" s="9"/>
       <c r="D123" s="8">
-        <v>46223.59539700231</v>
+        <v>46283.15218138889</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>385</v>
@@ -8947,8 +8947,8 @@
       <c r="S123" s="9">
         <v>0</v>
       </c>
-      <c r="T123" s="11" t="s">
-        <v>127</v>
+      <c r="T123" s="12" t="s">
+        <v>356</v>
       </c>
       <c r="U123" s="10" t="s">
         <v>53</v>
